--- a/Сравнение_КП_959777517.xlsx
+++ b/Сравнение_КП_959777517.xlsx
@@ -7,9 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сравнение" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сравнение КП" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Позиции КП" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Конкурентная карта" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Итоги поставщиков" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Заключение" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сравнение КП'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Позиции КП'!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Конкурентная карта'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Итоги поставщиков'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Заключение'!$A$1:$B$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +35,34 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +70,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,107 +467,3352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>№ КП</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>НДС</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Доставка</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Срок поставки</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>120 048,30</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>включён</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>срок резервирования товара 3 рабочих дня</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Оплата означает согласие с условиями поставки. Товар отпускается по факту прихода денег. Уведомление об оплате обязательно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>122 072,00 ₽</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>включён</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>самовывоз</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>от 5 до 7 раб.дн.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Доставка самовывозом из г. Челябинск, ул. Комарова, д. 110. Срок поставки указан для всех позиций от 5 до 7 рабочих дней. НДС включён, сумма НДС 22 012,98 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>168 824,00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>включён</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>самовывоз</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>счет действителен 7 календарных дней</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Оплата означает согласие с условиями поставки. Товар отпускается по факту прихода денег на р/с поставщика, при наличии доверенности и паспорта. Срок поставки не указан явно.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Файл</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Краткий вывод ИИ</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ключ позиции</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Сумма</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>КП МКА ООО.pdf</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1. Краткий итог сравнения  
-Два предложения на АКБ 24V 375Ah: ООО "МКА" — 137 000 руб без доставки, самовывоз, оплата до 14.04.2026, ООО "Тюмень-Индастриал" — 114 800 руб с НДС, доставка до терминала в Челябинске за 1 неделю, 100% предоплата.  
-2. КП №1 — ООО "МКА"  
-- Сумма: 137 000 руб (НДС 22% включен)  
-- Срок оплаты: до 14.04.2026  
-- Доставка: нет, самовывоз со склада в Московской обл., Ступино  
-- НДС: 22% включен (24 705 руб)  
-- Важные условия: товар отпускается после оплаты, обязательное уведомление об оплате, необходимость доверенности и паспорта для получения  
-КП №2 — ООО "Тюмень-Индастриал"  
-- Сумма: 114 800 руб с НДС  
-- Срок поставки: 1 неделя  
-- Доставка: на терминал ТК "Деловые линии" в Челябинске  
-- НДС: 22% включен  
-- Важные условия: 100% предоплата, гарантия 24 месяца, срок службы не менее 1500 циклов, сертификаты и ТУ указаны, изготовитель АО «Тюменский аккумуляторный завод»  
-3. Самое выгодное предложение  
-ООО "Тюмень-Индастриал" — цена ниже на 22 200 руб, плюс доставка до терминала включена, гарантия 24 месяца и подтверждённый производитель.  
-4. Риски и аномалии  
-- "МКА" не включает доставку, сроки поставки не указаны, требуется самовывоз из Московской области — дополнительные затраты времени и транспорта.  
-- ООО "МКА" требует оплату до 14.04.2026, что скоро, может быть спешка.  
-- "Тюмень-Индастриал" требует 100% предоплату без отсрочки, что увеличивает финансовый риск.  
-- В КП "МКА" нет гарантии и технических данных, есть риск качества и срока службы.  
-5. Вопросы для поставщиков  
-- Для "МКА": какой срок поставки? Возможна ли доставка на объект? Гарантийные обязательства по АКБ?  
-- Для "Тюмень-Индастриал": можно ли обсудить условия оплаты (например, предоплата 50%)? Возможна ли доставка "до склада заказчика" или на объект? Есть ли гарантия на подряд и сервисное обслуживание?  
-6. Рекомендация для закупщика  
-Рекомендуется уточнить у "Тюмень-Индастриал" возможность более гибких условий оплаты и доставки, чтобы снизить финансовый риск и получить товар непосредственно на объект. При положительном ответе оформить заказ у "Тюмень-Индастриал" как более выгодного и технически обеспеченного поставщика. Если условия оплаты не устраивают, попросить подробнее у "МКА" про сроки и гарантию, но с прицелом на большую сумму и логистику.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CKB3-TWN3242-43</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB3-TWN3242-43 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2720,11</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2720,11</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB3-205</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB3-205 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>9995,48</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>9995,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CKB4-TWN4154-50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB4-TWN4154-50 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2969,18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2969,18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>CKB5-TWN5372-60</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB5-TWN5372-60 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3774,23</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3774,23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-245</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB5-245 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-165</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB5-165 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8900,10</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8900,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN115150-75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB6-TWN115150-75 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8529,30</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8529,30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-165 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8900,10</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8900,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-285</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-285 ACCKee</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13966,30</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13966,30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN89120-75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB6-TWN89120-75 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5283,82</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5283,82</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-205</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-205 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN6890-75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB6-TWN6890-75 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5032,21</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5032,21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-125</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-125 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7667,77</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7667,77</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-245</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-245 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11090,89</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11090,89</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB4-245</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB4-245 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>CKB3-TWN3242-43</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Расточная головка CKB3-TWN3242-43 bh00018</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5205,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5205,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB3-205</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Оправка для расточных головок BT50-CKB3-205 sh00098</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19127,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>19127,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>BESTE Штревель BT50-45 AC00601921</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>931,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2793,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>CKB4-TWN4154-50</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Расточная головка CKB4-TWN4154-50 bh00015</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5682,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5682,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>CKB5-TWN5372-60</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Расточная головка CKB5-TWN5372-60 bh00001</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>5883,00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5883,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-285</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Оправка для расточных головок BT50-CKB6-285 db01991</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>21498,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>21498,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB1-165</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>16134,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>16134,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN115150-75</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Расточная головка CKB6-TWN115150-75 bh00003</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>17180,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>17180,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-165</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Оправка BT50-CKB6-165 sh00023</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17927,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>17927,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN89120-75</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Расточная головка CKB6-TWN89120-75 bh00002</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>10643,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10643,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>CKB3-TWN3242-43</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CKB3-TWN3242-43 черновая расточная головка</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3 710,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>3 710,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB3-205</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB3-205 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>8 980,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8 980,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45T</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Штревель BT50-45T (с СОЖ)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CKB4-TWN4154-50</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CKB4-TWN4154-50 черновая расточная головка</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>4 430,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4 430,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45T</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Штревель BT50-45T (с СОЖ)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>CKB5-TWN5372-60</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>CKB5-TWN5372-60 черновая расточная головка</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>4 730,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>4 730,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-285</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-285 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>10 940,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>10 940,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-165</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-165 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>10 340,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>10 340,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45T</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Штревель BT50-45T (с СОЖ)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN115150-75</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN115150-75 черновая расточная головка</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>9 450,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>9 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-165</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-165 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>10 340,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>10 340,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-285</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-285 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>12 560,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12 560,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45T</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Штревель BT50-45T (с СОЖ)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN89120-75</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN89120-75 черновая расточная головка</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>6 620,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>6 620,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-205</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-205 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>9 380,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>9 380,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45T</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Штревель BT50-45T (с СОЖ)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>RDH-D151-211-80L</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>RDH-D151-211-80L черновая расточная головка</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>14 250,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>14 250,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45T</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Штревель BT50-45T (с СОЖ)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN6890-75</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN6890-75 черновая расточная головка</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>6 300,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>6 300,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-125</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-125 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>6 890,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>6 890,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-245</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-245 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>9 990,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>9 990,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45T</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Штревель BT50-45T (с СОЖ)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB4-245</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB4-245 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>16 912,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>16 912,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>КП_Доминик_Счет_на_оплату_№_11282_от_25_03_2026_2_1.pdf</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>BT50-DM32-300</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>BT50-DM32-300 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>20 482,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>20 482,00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H50"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ключ позиции</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Победитель</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Мин. цена</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Макс. цена</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Экономия</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CKB3-TWN3242-43</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB3-TWN3242-43 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2720,11</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>5205,00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>3 710,00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2720.11</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5205</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2484.89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB3-205</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB3-205 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>9995,48</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>19127,00</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>8 980,00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>8980</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>19127</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>10147</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CKB4-TWN4154-50</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB4-TWN4154-50 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2969,18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5682,00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4 430,00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2969.18</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>5682</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2712.82</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CKB5-TWN5372-60</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB5-TWN5372-60 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>3774,23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5883,00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4 730,00</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>3774.23</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>5883</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>2108.77</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-245</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB5-245 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>10406.27</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>10406.27</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-165</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB5-165 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>8900,10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10 340,00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>8900.1</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>10340</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1439.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN115150-75</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB6-TWN115150-75 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>8529,30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17180,00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9 450,00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>8529.299999999999</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>17180</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>8650.700000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-165</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-165 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>8900,10</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17927,00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10 340,00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>8900.1</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>17927</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>9026.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-285</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-285 ACCKee</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13966,30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21498,00</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>12 560,00</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>12560</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>21498</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>8938</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN89120-75</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB6-TWN89120-75 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>5283,82</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10643,00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6 620,00</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>5283.82</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>10643</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>5359.18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-205</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-205 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>9 380,00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>9380</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>10406.27</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1026.27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CKB6-TWN6890-75</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Расточная головка CKB6-TWN6890-75 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>5032,21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6 300,00</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>5032.21</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>6300</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1267.79</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-125</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-125 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7667,77</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>6 890,00</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>6890</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>7667.77</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>777.7700000000004</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB6-245</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB6-245 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11090,89</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>9 990,00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>9990</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>11090.89</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1100.889999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB4-245</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Оправка для расточных головок BT50-CKB4-245 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16 912,00</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>10406.27</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>16912</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>6505.73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>BESTE Штревель BT50-45 AC00601921</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>931,00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>931</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>931</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB1-165</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>16134,00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>16134</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>16134</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BT50-45T</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Штревель BT50-45T (с СОЖ)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>360,00</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-285</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>BT50-CKB5-285 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>10 940,00</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>10940</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>10940</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RDH-D151-211-80L</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>RDH-D151-211-80L черновая расточная головка</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>14 250,00</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>14250</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>14250</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BT50-DM32-300</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>BT50-DM32-300 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>20 482,00</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>20482</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>20482</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Всего позиций в КП</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Позиций выиграно</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Сумма выигранных позиций</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>66921.59</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Лидер по количеству минимальных цен</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>КП Тюмень-Индастриал ООО.pdf</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1. Краткий итог сравнения  
-Два предложения на АКБ 24V 375Ah: ООО "МКА" — 137 000 руб без доставки, самовывоз, оплата до 14.04.2026, ООО "Тюмень-Индастриал" — 114 800 руб с НДС, доставка до терминала в Челябинске за 1 неделю, 100% предоплата.  
-2. КП №1 — ООО "МКА"  
-- Сумма: 137 000 руб (НДС 22% включен)  
-- Срок оплаты: до 14.04.2026  
-- Доставка: нет, самовывоз со склада в Московской обл., Ступино  
-- НДС: 22% включен (24 705 руб)  
-- Важные условия: товар отпускается после оплаты, обязательное уведомление об оплате, необходимость доверенности и паспорта для получения  
-КП №2 — ООО "Тюмень-Индастриал"  
-- Сумма: 114 800 руб с НДС  
-- Срок поставки: 1 неделя  
-- Доставка: на терминал ТК "Деловые линии" в Челябинске  
-- НДС: 22% включен  
-- Важные условия: 100% предоплата, гарантия 24 месяца, срок службы не менее 1500 циклов, сертификаты и ТУ указаны, изготовитель АО «Тюменский аккумуляторный завод»  
-3. Самое выгодное предложение  
-ООО "Тюмень-Индастриал" — цена ниже на 22 200 руб, плюс доставка до терминала включена, гарантия 24 месяца и подтверждённый производитель.  
-4. Риски и аномалии  
-- "МКА" не включает доставку, сроки поставки не указаны, требуется самовывоз из Московской области — дополнительные затраты времени и транспорта.  
-- ООО "МКА" требует оплату до 14.04.2026, что скоро, может быть спешка.  
-- "Тюмень-Индастриал" требует 100% предоплату без отсрочки, что увеличивает финансовый риск.  
-- В КП "МКА" нет гарантии и технических данных, есть риск качества и срока службы.  
-5. Вопросы для поставщиков  
-- Для "МКА": какой срок поставки? Возможна ли доставка на объект? Гарантийные обязательства по АКБ?  
-- Для "Тюмень-Индастриал": можно ли обсудить условия оплаты (например, предоплата 50%)? Возможна ли доставка "до склада заказчика" или на объект? Есть ли гарантия на подряд и сервисное обслуживание?  
-6. Рекомендация для закупщика  
-Рекомендуется уточнить у "Тюмень-Индастриал" возможность более гибких условий оплаты и доставки, чтобы снизить финансовый риск и получить товар непосредственно на объект. При положительном ответе оформить заказ у "Тюмень-Индастриал" как более выгодного и технически обеспеченного поставщика. Если условия оплаты не устраивают, попросить подробнее у "МКА" про сроки и гарантию, но с прицелом на большую сумму и логистику.</t>
+      <c r="D3" s="2" t="n">
+        <v>17065</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Лидер по количеству минимальных цен</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>93832</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Лидер по количеству минимальных цен</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Всего КП</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Всего уникальных позиций</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Лидер по минимальным ценам</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Потенциальная экономия</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>61546.60999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Рекомендация</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Текст заключения</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>По результатам анализа коммерческих предложений лидер по количеству минимальных цен — Общество с ограниченной ответственностью "ВОЛЬФСТАР". Рекомендуется дополнительно проверить сроки поставки, условия оплаты, наличие товара, гарантию и включение доставки.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Сравнение_КП_959777517.xlsx
+++ b/Сравнение_КП_959777517.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Заключение" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сравнение КП'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сравнение КП'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Позиции КП'!$A$1:$H$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Конкурентная карта'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Итоги поставщиков'!$A$1:$E$4</definedName>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,12 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +517,31 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Условия оплаты</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Гарантия</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Срок действия КП</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Страна</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Комментарий</t>
         </is>
       </c>
@@ -522,12 +552,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>120 048,30</t>
+          <t>122 072,00 ₽</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -537,17 +567,42 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>самовывоз</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>от 5 до 7 раб.дн.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>полная оплата счета, акцепт в течение 3 рабочих дней</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>срок резервирования товара 3 рабочих дня</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Оплата означает согласие с условиями поставки. Товар отпускается по факту прихода денег. Уведомление об оплате обязательно.</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>3 рабочих дня с даты выставления счета (26 марта 2026 года)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee, BESTE</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Доставка - самовывоз из г. Челябинск, ул. Комарова, д. 110. Гарантия не указана. Срок поставки от 5 до 7 рабочих дней. Оплата полная, акцепт оферты в течение 3 рабочих дней.</t>
         </is>
       </c>
     </row>
@@ -557,12 +612,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>122 072,00 ₽</t>
+          <t>120 048,30</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -572,17 +627,42 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>самовывоз</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>от 5 до 7 раб.дн.</t>
+          <t>срок резервирования товара 3 рабочих дня</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Доставка самовывозом из г. Челябинск, ул. Комарова, д. 110. Срок поставки указан для всех позиций от 5 до 7 рабочих дней. НДС включён, сумма НДС 22 012,98 ₽.</t>
+          <t>товар отпускается по факту прихода денег на р/с Поставщика</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Оплата означает согласие с условиями поставки. Уведомление об оплате обязательно. Гарантия и срок действия КП не указаны. Доставка не указана.</t>
         </is>
       </c>
     </row>
@@ -607,22 +687,47 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>самовывоз</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>счет действителен 7 календарных дней</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Оплата означает согласие с условиями поставки. Товар отпускается по факту прихода денег на р/с поставщика, при наличии доверенности и паспорта. Срок поставки не указан явно.</t>
+          <t>оплата по факту прихода денег на р/с Поставщика</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7 календарных дней</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Доставка не указана, гарантия не указана, производитель и страна не указаны.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -691,12 +796,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -706,7 +811,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB3-TWN3242-43 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB3-TWN3242-43 bh00018</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -721,24 +826,24 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2720,11</t>
+          <t>5205,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2720,11</t>
+          <t>5205,00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -748,7 +853,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB3-205 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB3-205 sh00098</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -763,34 +868,34 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>9995,48</t>
+          <t>19127,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>9995,48</t>
+          <t>19127,00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CKB4-TWN4154-50</t>
+          <t>BT50-45</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB4-TWN4154-50 "ACCKee"</t>
+          <t>BESTE Штревель BT50-45 AC00601921</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -800,39 +905,39 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2969,18</t>
+          <t>931,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2969,18</t>
+          <t>2793,00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CKB5-TWN5372-60</t>
+          <t>CKB4-TWN4154-50</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB5-TWN5372-60 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB4-TWN4154-50 bh00015</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -847,34 +952,34 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3774,23</t>
+          <t>5682,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3774,23</t>
+          <t>5682,00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB5-245</t>
+          <t>CKB5-TWN5372-60</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB5-245 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB5-TWN5372-60 bh00001</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -889,34 +994,34 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10406,27</t>
+          <t>5883,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10406,27</t>
+          <t>5883,00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB5-165</t>
+          <t>BT50-CKB6-285</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB5-165 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB6-285 db01991</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -931,34 +1036,34 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8900,10</t>
+          <t>21498,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8900,10</t>
+          <t>21498,00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN115150-75</t>
+          <t>BT50-CKB1-165</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN115150-75 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -973,34 +1078,34 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8529,30</t>
+          <t>16134,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8529,30</t>
+          <t>16134,00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-165</t>
+          <t>CKB6-TWN115150-75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-165 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB6-TWN115150-75 bh00003</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1015,34 +1120,34 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8900,10</t>
+          <t>17180,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8900,10</t>
+          <t>17180,00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-285</t>
+          <t>BT50-CKB6-165</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-285 ACCKee</t>
+          <t>ACCKee Оправка BT50-CKB6-165 sh00023</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1057,24 +1162,24 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13966,30</t>
+          <t>17927,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13966,30</t>
+          <t>17927,00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1084,7 +1189,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN89120-75 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB6-TWN89120-75 bh00002</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1099,12 +1204,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5283,82</t>
+          <t>10643,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5283,82</t>
+          <t>10643,00</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1226,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-205</t>
+          <t>CKB3-TWN3242-43</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-205 "ACCKee"</t>
+          <t>Расточная головка CKB3-TWN3242-43 "ACCKee"</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1141,12 +1246,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10406,27</t>
+          <t>2720,11</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10406,27</t>
+          <t>2720,11</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1268,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN6890-75</t>
+          <t>BT50-CKB3-205</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN6890-75 "ACCKee"</t>
+          <t>Оправка для расточных головок BT50-CKB3-205 "ACCKee"</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1183,12 +1288,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5032,21</t>
+          <t>9995,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5032,21</t>
+          <t>9995,48</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1310,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-125</t>
+          <t>CKB4-TWN4154-50</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-125 "ACCKee"</t>
+          <t>Расточная головка CKB4-TWN4154-50 "ACCKee"</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1225,12 +1330,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7667,77</t>
+          <t>2969,18</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7667,77</t>
+          <t>2969,18</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1352,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-245</t>
+          <t>CKB5-TWN5372-60</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-245 "ACCKee"</t>
+          <t>Расточная головка CKB5-TWN5372-60 "ACCKee"</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1267,12 +1372,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11090,89</t>
+          <t>3774,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11090,89</t>
+          <t>3774,23</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1394,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB4-245</t>
+          <t>BT50-CKB5-245</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB4-245 "ACCKee"</t>
+          <t>Оправка для расточных головок BT50-CKB5-245 "ACCKee"</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1321,22 +1426,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CKB3-TWN3242-43</t>
+          <t>BT50-CKB5-165</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB3-TWN3242-43 bh00018</t>
+          <t>Оправка для расточных головок BT50-CKB5-165 "ACCKee"</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1351,34 +1456,34 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5205,00</t>
+          <t>8900,10</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5205,00</t>
+          <t>8900,10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB3-205</t>
+          <t>CKB6-TWN115150-75</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB3-205 sh00098</t>
+          <t>Расточная головка CKB6-TWN115150-75 "ACCKee"</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1393,34 +1498,34 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19127,00</t>
+          <t>8529,30</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19127,00</t>
+          <t>8529,30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>BT50-45</t>
+          <t>BT50-CKB6-165</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>BESTE Штревель BT50-45 AC00601921</t>
+          <t>Оправка для расточных головок BT50-CKB6-165 "ACCKee"</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1430,39 +1535,39 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>931,00</t>
+          <t>8900,10</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2793,00</t>
+          <t>8900,10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CKB4-TWN4154-50</t>
+          <t>BT50-CKB6-285</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB4-TWN4154-50 bh00015</t>
+          <t>Оправка для расточных головок BT50-CKB6-285 ACCKee</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1477,34 +1582,34 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5682,00</t>
+          <t>13966,30</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5682,00</t>
+          <t>13966,30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CKB5-TWN5372-60</t>
+          <t>CKB6-TWN89120-75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB5-TWN5372-60 bh00001</t>
+          <t>Расточная головка CKB6-TWN89120-75 "ACCKee"</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1519,34 +1624,34 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5883,00</t>
+          <t>5283,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5883,00</t>
+          <t>5283,82</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-285</t>
+          <t>BT50-CKB6-205</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB6-285 db01991</t>
+          <t>Оправка для расточных головок BT50-CKB6-205 "ACCKee"</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1561,34 +1666,34 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21498,00</t>
+          <t>10406,27</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21498,00</t>
+          <t>10406,27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB1-165</t>
+          <t>CKB6-TWN6890-75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
+          <t>Расточная головка CKB6-TWN6890-75 "ACCKee"</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1603,34 +1708,34 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16134,00</t>
+          <t>5032,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16134,00</t>
+          <t>5032,21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN115150-75</t>
+          <t>BT50-CKB6-125</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB6-TWN115150-75 bh00003</t>
+          <t>Оправка для расточных головок BT50-CKB6-125 "ACCKee"</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1645,34 +1750,34 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17180,00</t>
+          <t>7667,77</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17180,00</t>
+          <t>7667,77</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-165</t>
+          <t>BT50-CKB6-245</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка BT50-CKB6-165 sh00023</t>
+          <t>Оправка для расточных головок BT50-CKB6-245 "ACCKee"</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1687,34 +1792,34 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17927,00</t>
+          <t>11090,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17927,00</t>
+          <t>11090,89</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN89120-75</t>
+          <t>BT50-CKB4-245</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB6-TWN89120-75 bh00002</t>
+          <t>Оправка для расточных головок BT50-CKB4-245 "ACCKee"</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1729,12 +1834,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10643,00</t>
+          <t>10406,27</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10643,00</t>
+          <t>10406,27</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2892,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2829,17 +2934,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB3-TWN3242-43 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+          <t>ACCKee Расточная головка CKB3-TWN3242-43 bh00018</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>5205,00</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>2720,11</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>5205,00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2870,17 +2975,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB3-205 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB3-205 sh00098</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>19127,00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>9995,48</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>19127,00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2906,68 +3011,60 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CKB4-TWN4154-50</t>
+          <t>BT50-45</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB4-TWN4154-50 "ACCKee"</t>
+          <t>BESTE Штревель BT50-45 AC00601921</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2969,18</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5682,00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4 430,00</t>
-        </is>
-      </c>
+          <t>931,00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2969.18</v>
+        <v>931</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5682</v>
+        <v>931</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2712.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CKB5-TWN5372-60</t>
+          <t>CKB4-TWN4154-50</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB5-TWN5372-60 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>3774,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5883,00</t>
+          <t>ACCKee Расточная головка CKB4-TWN4154-50 bh00015</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5682,00</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2969,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4 730,00</t>
+          <t>4 430,00</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2976,150 +3073,154 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3774.23</v>
+        <v>2969.18</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5883</v>
+        <v>5682</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2108.77</v>
+        <v>2712.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB5-245</t>
+          <t>CKB5-TWN5372-60</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB5-245 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>10406,27</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>ACCKee Расточная головка CKB5-TWN5372-60 bh00001</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5883,00</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>3774,23</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4 730,00</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10406.27</v>
+        <v>3774.23</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10406.27</v>
+        <v>5883</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>2108.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB5-165</t>
+          <t>BT50-CKB6-285</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB5-165 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>8900,10</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10 340,00</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB6-285 db01991</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>21498,00</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13966,30</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>12 560,00</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО "ДОМИНИК"</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8900.1</v>
+        <v>12560</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10340</v>
+        <v>21498</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1439.9</v>
+        <v>8938</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN115150-75</t>
+          <t>BT50-CKB1-165</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN115150-75 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>8529,30</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>17180,00</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9 450,00</t>
-        </is>
-      </c>
+          <t>16134,00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8529.299999999999</v>
+        <v>16134</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>17180</v>
+        <v>16134</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8650.700000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-165</t>
+          <t>CKB6-TWN115150-75</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-165 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>8900,10</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>17927,00</t>
+          <t>ACCKee Расточная головка CKB6-TWN115150-75 bh00003</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>17180,00</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>8529,30</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10 340,00</t>
+          <t>9 450,00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -3128,54 +3229,54 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8900.1</v>
+        <v>8529.299999999999</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17927</v>
+        <v>17180</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>9026.9</v>
+        <v>8650.700000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-285</t>
+          <t>BT50-CKB6-165</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-285 ACCKee</t>
+          <t>ACCKee Оправка BT50-CKB6-165 sh00023</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13966,30</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21498,00</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>12 560,00</t>
+          <t>17927,00</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>8900,10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10 340,00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ООО "ДОМИНИК"</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>12560</v>
+        <v>8900.1</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>21498</v>
+        <v>17927</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>8938</v>
+        <v>9026.9</v>
       </c>
     </row>
     <row r="11">
@@ -3186,17 +3287,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN89120-75 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+          <t>ACCKee Расточная головка CKB6-TWN89120-75 bh00002</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10643,00</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>5283,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10643,00</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3222,60 +3323,56 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-205</t>
+          <t>BT50-CKB5-245</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-205 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+          <t>Оправка для расточных головок BT50-CKB5-245 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>10406,27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>9 380,00</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ООО "ДОМИНИК"</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>9380</v>
+        <v>10406.27</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>10406.27</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1026.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN6890-75</t>
+          <t>BT50-CKB5-165</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN6890-75 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>5032,21</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
+          <t>Оправка для расточных головок BT50-CKB5-165 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>8900,10</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6 300,00</t>
+          <t>10 340,00</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3284,35 +3381,35 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5032.21</v>
+        <v>8900.1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6300</v>
+        <v>10340</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1267.79</v>
+        <v>1439.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-125</t>
+          <t>BT50-CKB6-205</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-125 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>7667,77</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Оправка для расточных головок BT50-CKB6-205 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>6 890,00</t>
+          <t>9 380,00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3321,153 +3418,161 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>6890</v>
+        <v>9380</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>7667.77</v>
+        <v>10406.27</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>777.7700000000004</v>
+        <v>1026.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-245</t>
+          <t>CKB6-TWN6890-75</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-245 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>11090,89</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>9 990,00</t>
+          <t>Расточная головка CKB6-TWN6890-75 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>5032,21</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6 300,00</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>ООО "ДОМИНИК"</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>9990</v>
+        <v>5032.21</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>11090.89</v>
+        <v>6300</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1100.889999999999</v>
+        <v>1267.79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB4-245</t>
+          <t>BT50-CKB6-125</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB4-245 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>10406,27</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16 912,00</t>
+          <t>Оправка для расточных головок BT50-CKB6-125 "ACCKee"</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7667,77</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>6 890,00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО "ДОМИНИК"</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>10406.27</v>
+        <v>6890</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16912</v>
+        <v>7667.77</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6505.73</v>
+        <v>777.7700000000004</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BT50-45</t>
+          <t>BT50-CKB6-245</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>BESTE Штревель BT50-45 AC00601921</t>
+          <t>Оправка для расточных головок BT50-CKB6-245 "ACCKee"</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>931,00</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11090,89</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>9 990,00</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>ООО "ДОМИНИК"</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>931</v>
+        <v>9990</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>931</v>
+        <v>11090.89</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1100.889999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB1-165</t>
+          <t>BT50-CKB4-245</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
+          <t>Оправка для расточных головок BT50-CKB4-245 "ACCKee"</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>16134,00</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>10406,27</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16 912,00</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>16134</v>
+        <v>10406.27</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>16134</v>
+        <v>16912</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>6505.73</v>
       </c>
     </row>
     <row r="19">
@@ -3652,42 +3757,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ООО «ВсеИнструменты.ру»</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>17065</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Лидер по количеству минимальных цен</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>66921.59</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Лидер по количеству минимальных цен</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>17065</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Лидер по количеству минимальных цен</t>
         </is>
@@ -3784,7 +3889,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>61546.60999999999</v>
+        <v>61546.61</v>
       </c>
     </row>
     <row r="6">

--- a/Сравнение_КП_959777517.xlsx
+++ b/Сравнение_КП_959777517.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сравнение КП'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Позиции КП'!$A$1:$H$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Конкурентная карта'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Конкурентная карта'!$A$1:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Итоги поставщиков'!$A$1:$E$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Заключение'!$A$1:$B$8</definedName>
   </definedNames>
@@ -552,12 +552,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>122 072,00 ₽</t>
+          <t>120 048,30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -567,17 +567,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>самовывоз</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>от 5 до 7 раб.дн.</t>
+          <t>срок резервирования товара 3 рабочих дня</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>полная оплата счета, акцепт в течение 3 рабочих дней</t>
+          <t>товар отпускается по факту прихода денег на р/с Поставщика</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3 рабочих дня с даты выставления счета (26 марта 2026 года)</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ACCKee, BESTE</t>
+          <t>ACCKee</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Доставка - самовывоз из г. Челябинск, ул. Комарова, д. 110. Гарантия не указана. Срок поставки от 5 до 7 рабочих дней. Оплата полная, акцепт оферты в течение 3 рабочих дней.</t>
+          <t>Оплата означает согласие с условиями поставки. Уведомление об оплате обязательно, иначе наличие товара не гарантируется.</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>120 048,30</t>
+          <t>122 072,00 ₽</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -627,42 +627,42 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>самовывоз</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>от 5 до 7 раб.дн.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>полная оплата счета, акцепт в течение 3 рабочих дней</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>срок резервирования товара 3 рабочих дня</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>товар отпускается по факту прихода денег на р/с Поставщика</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>3 рабочих дня с даты выставления счета (26 марта 2026 года)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ACCKee, BESTE</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>не указано</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>ACCKee</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Оплата означает согласие с условиями поставки. Уведомление об оплате обязательно. Гарантия и срок действия КП не указаны. Доставка не указана.</t>
+          <t>Доставка - самовывоз из г. Челябинск, ул. Комарова, д. 110. Гарантия не указана. Срок поставки от 5 до 7 рабочих дней. Оплата полная, акцепт оферты в течение 3 рабочих дней.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Доставка не указана, гарантия не указана, производитель и страна не указаны.</t>
+          <t>Доставка не указана. Гарантия не указана. Производитель и страна происхождения не указаны.</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB3-TWN3242-43 bh00018</t>
+          <t>Расточная головка CKB3-TWN3242-43</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -821,29 +821,29 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>5205,00</t>
+          <t>2720,11</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>5205,00</t>
+          <t>2720,11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB3-205 sh00098</t>
+          <t>Оправка для расточных головок BT50-CKB3-205</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -863,39 +863,39 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>19127,00</t>
+          <t>9995,48</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>19127,00</t>
+          <t>9995,48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BT50-45</t>
+          <t>CKB4-TWN4154-50</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>BESTE Штревель BT50-45 AC00601921</t>
+          <t>Расточная головка CKB4-TWN4154-50</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -905,39 +905,39 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>931,00</t>
+          <t>2969,18</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2793,00</t>
+          <t>2969,18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CKB4-TWN4154-50</t>
+          <t>CKB5-TWN5372-60</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB4-TWN4154-50 bh00015</t>
+          <t>Расточная головка CKB5-TWN5372-60</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -947,39 +947,39 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5682,00</t>
+          <t>3774,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5682,00</t>
+          <t>не указано</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CKB5-TWN5372-60</t>
+          <t>BT50-CKB5-245</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB5-TWN5372-60 bh00001</t>
+          <t>Оправка для расточных головок BT50-CKB5-245</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -989,39 +989,39 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5883,00</t>
+          <t>406,27</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5883,00</t>
+          <t>4062,7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-285</t>
+          <t>СКВ5-165</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB6-285 db01991</t>
+          <t>Оправка для расточных головок ВТ50-СКВ5-165</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1031,39 +1031,39 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21498,00</t>
+          <t>900,10</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21498,00</t>
+          <t>7200,8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB1-165</t>
+          <t>CKB6-TWN115150-75</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
+          <t>Расточная головка CKB6-TWN115150-75</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1073,39 +1073,39 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16134,00</t>
+          <t>8529,30</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16134,00</t>
+          <t>не указано</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN115150-75</t>
+          <t>BT50-CKB6-165</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB6-TWN115150-75 bh00003</t>
+          <t>Оправка для расточных головок BT50-CKB6-165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1115,39 +1115,39 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17180,00</t>
+          <t>900,10</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17180,00</t>
+          <t>не указано</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-165</t>
+          <t>BT50-CKB6-285</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка BT50-CKB6-165 sh00023</t>
+          <t>Оправка для расточных головок BT50-CKB6-285</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1157,29 +1157,29 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17927,00</t>
+          <t>13966,30</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17927,00</t>
+          <t>13966,30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB6-TWN89120-75 bh00002</t>
+          <t>Расточная головка CKB6-TWN89120-75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1199,24 +1199,24 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10643,00</t>
+          <t>5283,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10643,00</t>
+          <t>5283,82</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CKB3-TWN3242-43</t>
+          <t>BT50-CKB6-205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB3-TWN3242-43 "ACCKee"</t>
+          <t>Оправка для расточных головок BT50-CKB6-205</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1241,24 +1241,24 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2720,11</t>
+          <t>406,27</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2720,11</t>
+          <t>4062,7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB3-205</t>
+          <t>CKB6-TWN6890-75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB3-205 "ACCKee"</t>
+          <t>Расточная головка CKB6-TWN6890-75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1283,24 +1283,24 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9995,48</t>
+          <t>5032,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9995,48</t>
+          <t>5032,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CKB4-TWN4154-50</t>
+          <t>BT50-CKB6-125</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB4-TWN4154-50 "ACCKee"</t>
+          <t>Оправка для расточных головок BT50-CKB6-125</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1325,24 +1325,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2969,18</t>
+          <t>7667,77</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2969,18</t>
+          <t>7667,77</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CKB5-TWN5372-60</t>
+          <t>BT50-CKB6-245</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB5-TWN5372-60 "ACCKee"</t>
+          <t>Оправка для расточных головок BT50-CKB6-245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1367,24 +1367,24 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3774,23</t>
+          <t>11090,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3774,23</t>
+          <t>11090,89</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>doc01972620260520192040.pdf</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB5-245</t>
+          <t>BT50-CKB4-245</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB5-245 "ACCKee"</t>
+          <t>Оправка для расточных головок BT50-CKB4-245</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB5-165</t>
+          <t>CKB3-TWN3242-43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB5-165 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB3-TWN3242-43 bh00018</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1456,34 +1456,34 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8900,10</t>
+          <t>5205,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8900,10</t>
+          <t>5205,00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN115150-75</t>
+          <t>BT50-CKB3-205</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN115150-75 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB3-205 sh00098</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1498,34 +1498,34 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8529,30</t>
+          <t>19127,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8529,30</t>
+          <t>19127,00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-165</t>
+          <t>BT50-45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-165 "ACCKee"</t>
+          <t>BESTE Штревель BT50-45 AC00601921</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1535,39 +1535,39 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8900,10</t>
+          <t>931,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8900,10</t>
+          <t>2793,00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-285</t>
+          <t>CKB4-TWN4154-50</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-285 ACCKee</t>
+          <t>ACCKee Расточная головка CKB4-TWN4154-50 bh00015</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1582,34 +1582,34 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13966,30</t>
+          <t>5682,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13966,30</t>
+          <t>5682,00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN89120-75</t>
+          <t>CKB5-TWN5372-60</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN89120-75 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB5-TWN5372-60 bh00001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1624,34 +1624,34 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5283,82</t>
+          <t>5883,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5283,82</t>
+          <t>5883,00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-205</t>
+          <t>BT50-CKB6-285</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-205 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB6-285 db01991</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1666,34 +1666,34 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10406,27</t>
+          <t>21498,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10406,27</t>
+          <t>21498,00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN6890-75</t>
+          <t>BT50-CKB1-165</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN6890-75 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1708,34 +1708,34 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5032,21</t>
+          <t>16134,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5032,21</t>
+          <t>16134,00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-125</t>
+          <t>CKB6-TWN115150-75</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-125 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB6-TWN115150-75 bh00003</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1750,34 +1750,34 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7667,77</t>
+          <t>17180,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7667,77</t>
+          <t>17180,00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-245</t>
+          <t>BT50-CKB6-165</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-245 "ACCKee"</t>
+          <t>ACCKee Оправка BT50-CKB6-165 sh00023</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1792,34 +1792,34 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11090,89</t>
+          <t>17927,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11090,89</t>
+          <t>17927,00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>КП_Вольфстар_ООО_Счет_на_оплату_№_856_от_26_марта_2026_г_1.pdf</t>
+          <t>КП_Все_инструменты_ООО_Счет_на_оплату_№2603_453438_40628.pdf</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB4-245</t>
+          <t>CKB6-TWN89120-75</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB4-245 "ACCKee"</t>
+          <t>ACCKee Расточная головка CKB6-TWN89120-75 bh00002</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10406,27</t>
+          <t>10643,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10406,27</t>
+          <t>10643,00</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ООО «ВсеИнструменты.ру»</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB3-TWN3242-43 bh00018</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+          <t>Расточная головка CKB3-TWN3242-43</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2720,11</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>5205,00</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2720,11</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2975,17 +2975,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB3-205 sh00098</t>
+          <t>Оправка для расточных головок BT50-CKB3-205</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>9995,48</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>19127,00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>9995,48</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -3011,60 +3011,68 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BT50-45</t>
+          <t>CKB4-TWN4154-50</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BESTE Штревель BT50-45 AC00601921</t>
+          <t>Расточная головка CKB4-TWN4154-50</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>931,00</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>2969,18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5682,00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4 430,00</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>931</v>
+        <v>2969.18</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>931</v>
+        <v>5682</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>2712.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CKB4-TWN4154-50</t>
+          <t>CKB5-TWN5372-60</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB4-TWN4154-50 bh00015</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5682,00</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2969,18</t>
+          <t>Расточная головка CKB5-TWN5372-60</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>3774,23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5883,00</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4 430,00</t>
+          <t>4 730,00</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3073,154 +3081,146 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2969.18</v>
+        <v>3774.23</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5682</v>
+        <v>5883</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2712.82</v>
+        <v>2108.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CKB5-TWN5372-60</t>
+          <t>BT50-CKB5-245</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB5-TWN5372-60 bh00001</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5883,00</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>3774,23</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4 730,00</t>
-        </is>
-      </c>
+          <t>Оправка для расточных головок BT50-CKB5-245</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>406,27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3774.23</v>
+        <v>406.27</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5883</v>
+        <v>406.27</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2108.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-285</t>
+          <t>СКВ5-165</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB6-285 db01991</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>21498,00</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13966,30</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>12 560,00</t>
-        </is>
-      </c>
+          <t>Оправка для расточных головок ВТ50-СКВ5-165</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>900,10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ООО "ДОМИНИК"</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>12560</v>
+        <v>900.1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>21498</v>
+        <v>900.1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>8938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB1-165</t>
+          <t>CKB6-TWN115150-75</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
+          <t>Расточная головка CKB6-TWN115150-75</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>16134,00</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>8529,30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17180,00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9 450,00</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>ООО «ВсеИнструменты.ру»</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>16134</v>
+        <v>8529.299999999999</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>16134</v>
+        <v>17180</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>8650.700000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN115150-75</t>
+          <t>BT50-CKB6-165</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB6-TWN115150-75 bh00003</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>17180,00</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>8529,30</t>
+          <t>Оправка для расточных головок BT50-CKB6-165</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>900,10</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17927,00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9 450,00</t>
+          <t>10 340,00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -3229,54 +3229,54 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8529.299999999999</v>
+        <v>900.1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17180</v>
+        <v>17927</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8650.700000000001</v>
+        <v>17026.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-165</t>
+          <t>BT50-CKB6-285</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Оправка BT50-CKB6-165 sh00023</t>
+          <t>Оправка для расточных головок BT50-CKB6-285</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17927,00</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>8900,10</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10 340,00</t>
+          <t>13966,30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21498,00</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>12 560,00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО "ДОМИНИК"</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8900.1</v>
+        <v>12560</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17927</v>
+        <v>21498</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>9026.9</v>
+        <v>8938</v>
       </c>
     </row>
     <row r="11">
@@ -3287,17 +3287,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ACCKee Расточная головка CKB6-TWN89120-75 bh00002</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+          <t>Расточная головка CKB6-TWN89120-75</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>5283,82</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>10643,00</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>5283,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3323,56 +3323,60 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB5-245</t>
+          <t>BT50-CKB6-205</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB5-245 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>10406,27</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>Оправка для расточных головок BT50-CKB6-205</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>406,27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9 380,00</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10406.27</v>
+        <v>406.27</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10406.27</v>
+        <v>9380</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>8973.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB5-165</t>
+          <t>CKB6-TWN6890-75</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB5-165 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>8900,10</t>
-        </is>
-      </c>
+          <t>Расточная головка CKB6-TWN6890-75</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>5032,21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10 340,00</t>
+          <t>6 300,00</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3381,35 +3385,35 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8900.1</v>
+        <v>5032.21</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10340</v>
+        <v>6300</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1439.9</v>
+        <v>1267.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-205</t>
+          <t>BT50-CKB6-125</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-205 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>10406,27</t>
-        </is>
-      </c>
+          <t>Оправка для расточных головок BT50-CKB6-125</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7667,77</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>9 380,00</t>
+          <t>6 890,00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3418,161 +3422,153 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9380</v>
+        <v>6890</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10406.27</v>
+        <v>7667.77</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1026.27</v>
+        <v>777.7700000000004</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CKB6-TWN6890-75</t>
+          <t>BT50-CKB6-245</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Расточная головка CKB6-TWN6890-75 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>5032,21</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>6 300,00</t>
+          <t>Оправка для расточных головок BT50-CKB6-245</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11090,89</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>9 990,00</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО "ДОМИНИК"</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5032.21</v>
+        <v>9990</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>6300</v>
+        <v>11090.89</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1267.79</v>
+        <v>1100.889999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-125</t>
+          <t>BT50-CKB4-245</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-125 "ACCKee"</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7667,77</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>6 890,00</t>
+          <t>Оправка для расточных головок BT50-CKB4-245</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>10406,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16 912,00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>ООО "ДОМИНИК"</t>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6890</v>
+        <v>10406.27</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>7667.77</v>
+        <v>16912</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>777.7700000000004</v>
+        <v>6505.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB6-245</t>
+          <t>BT50-45</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB6-245 "ACCKee"</t>
+          <t>BESTE Штревель BT50-45 AC00601921</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>11090,89</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>9 990,00</t>
-        </is>
-      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>931,00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>ООО "ДОМИНИК"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>9990</v>
+        <v>931</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>11090.89</v>
+        <v>931</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1100.889999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BT50-CKB4-245</t>
+          <t>BT50-CKB1-165</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Оправка для расточных головок BT50-CKB4-245 "ACCKee"</t>
+          <t>ACCKee Оправка для расточных головок BT50-CKB1-165 sh00095</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>10406,27</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>16 912,00</t>
-        </is>
-      </c>
+          <t>16134,00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+          <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>10406.27</v>
+        <v>16134</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>16912</v>
+        <v>16134</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6505.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3644,19 +3640,19 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RDH-D151-211-80L</t>
+          <t>BT50-CKB5-165</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>RDH-D151-211-80L черновая расточная головка</t>
+          <t>BT50-CKB5-165 оправка для расточных систем</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>14 250,00</t>
+          <t>10 340,00</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3665,10 +3661,10 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>14250</v>
+        <v>10340</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>14250</v>
+        <v>10340</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
@@ -3677,19 +3673,19 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BT50-DM32-300</t>
+          <t>RDH-D151-211-80L</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BT50-DM32-300 оправка для расточных систем</t>
+          <t>RDH-D151-211-80L черновая расточная головка</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>20 482,00</t>
+          <t>14 250,00</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3698,17 +3694,50 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20482</v>
+        <v>14250</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>20482</v>
+        <v>14250</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>BT50-DM32-300</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BT50-DM32-300 оправка для расточных систем</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>20 482,00</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>ООО "ДОМИНИК"</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>20482</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>20482</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3757,42 +3786,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>41327.86</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Лидер по количеству минимальных цен</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ООО «ВсеИнструменты.ру»</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D3" s="2" t="n">
         <v>17065</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Лидер по количеству минимальных цен</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Общество с ограниченной ответственностью "ВОЛЬФСТАР"</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>66921.59</v>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Лидер по количеству минимальных цен</t>
         </is>
@@ -3811,7 +3840,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>93832</v>
+        <v>94792</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3867,7 +3896,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -3889,7 +3918,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>61546.61</v>
+        <v>76054.17</v>
       </c>
     </row>
     <row r="6">
